--- a/output/pdf_financials_xlsx/JAEG.H.xlsx
+++ b/output/pdf_financials_xlsx/JAEG.H.xlsx
@@ -5800,43 +5800,43 @@
         <v>3.307497</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.307497</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.307497</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.307497</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.307497</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.307497</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.307497</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.307497</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.307497</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.307497</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.307497</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.307497</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.307497</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.307497</v>
       </c>
     </row>
     <row r="93">
@@ -7193,43 +7193,43 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-1.582949</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.5187040000000001</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>4.820962</v>
+        <v>4.65776</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>6.148385</v>
+        <v>6.135669</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.029146</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>4.634659</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.036654</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.017547</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.02744</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.014091</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.002349</v>
       </c>
       <c r="O118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.374426</v>
+        <v>0.360712</v>
       </c>
       <c r="Q118" s="3" t="n">
         <v>0</v>
@@ -9250,7 +9250,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -10274,7 +10278,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -11932,7 +11940,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -15812,7 +15824,11 @@
           <t>Exploration and evaluation asset expenditures (Note 3)</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -17166,7 +17182,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/JAEG.H.xlsx
+++ b/output/pdf_financials_xlsx/JAEG.H.xlsx
@@ -946,19 +946,19 @@
         <v>0.06929200000000001</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.061905</v>
+        <v>0.088645</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.08260099999999999</v>
+        <v>0.108195</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.06714000000000001</v>
+        <v>0.096029</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.097271</v>
+        <v>0.500197</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.141851</v>
+        <v>0.241689</v>
       </c>
     </row>
     <row r="11">
@@ -1009,13 +1009,13 @@
         <v>-0.06929200000000001</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.061905</v>
+        <v>-0.088645</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.08260099999999999</v>
+        <v>-0.108195</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.06714000000000001</v>
+        <v>-0.096029</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>-0.500197</v>
@@ -2393,46 +2393,46 @@
         <v>0.209656</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.163072</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.089686</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.010853</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000794</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.005089</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.005852</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.009474</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.001995</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000867</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>7.6e-05</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>3.4e-05</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.041452</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.001237</v>
       </c>
     </row>
     <row r="35">
@@ -2505,46 +2505,46 @@
         <v>0.209656</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.163072</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.089686</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.010853</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000794</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.005089</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.005852</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.009474</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.001995</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000867</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>7.6e-05</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>3.4e-05</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.041452</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.001237</v>
       </c>
     </row>
     <row r="37">
@@ -3185,43 +3185,43 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.172664</v>
+        <v>0.009592</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.089686</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.010853</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.000794</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.005089</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.029091</v>
+        <v>0.023239</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.013057</v>
+        <v>0.003583</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.001728</v>
+        <v>0.0015</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.035895</v>
+        <v>0.0339</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.034767</v>
+        <v>0.0339</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.033976</v>
+        <v>0.0339</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.033934</v>
+        <v>0.0339</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.150532</v>
+        <v>0.10908</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -25842,7 +25842,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -26130,7 +26130,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -30746,7 +30746,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -31588,7 +31588,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -32434,7 +32434,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -33938,7 +33938,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">

--- a/output/pdf_financials_xlsx/JAEG.H.xlsx
+++ b/output/pdf_financials_xlsx/JAEG.H.xlsx
@@ -6875,10 +6875,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.0483</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.024035</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -20640,7 +20640,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
